--- a/data/LSR6_H_SOE.xlsx
+++ b/data/LSR6_H_SOE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/FS/HomeDrives/vc18e501/Biostatistics and Research Methods group/GALENOS - WP2/WP2/LSR6 Cognitive bias/LSR6_CBM_H/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jayceekennett/Documents/GitHub/LSR6_CBM_H/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8BF5CF-DDBC-3C47-A3C8-5F303DA4D287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6413AAE6-6D0E-C849-BB4D-14787B9173E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33980" yWindow="5020" windowWidth="28800" windowHeight="16040" xr2:uid="{5DFD502E-A31E-49FB-8319-0D4BC84D7C87}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17120" xr2:uid="{5DFD502E-A31E-49FB-8319-0D4BC84D7C87}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet11" sheetId="11" r:id="rId1"/>
@@ -107,26 +107,6 @@
     <t>Some concerns: using the ROB-MEN tool, this comparison was rated as some concerns, with substantial bias favouring CBM-I</t>
   </si>
   <si>
-    <t xml:space="preserve">N=19, n=1092;  SMD= -0.18  (95% CI: -0.41 to -0.05, 95% PI: -0.76 to 1.12)
-Using CINeMA, this comparisons was rated as some concerns for heterogeneity. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">N=4, n=272;  SMD= -0.01  (95% CI: -0.47 to 0.45, 95% PI: -0.26 to 1.04)
-Using CINeMA, this comparisons was rated as no concerns for heterogeneity. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">N=7, n=534;  SMD= -0.47  (95% CI: -0.84 to 0.09, 95% PI: -0.53 to 1.46)
-Using CINeMA, this comparisons was rated as major concerns for heterogeneity. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">N=1, n=42;  SMD= -0.71  (95% CI: -1.79 to 0.37, 95% PI: -0.73 to 2.15)
-Using CINeMA, this comparisons was rated as no concerns for heterogeneity. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">N=1, n=41;  SMD= -0.66  (95% CI: -1.29 to 0.07, 95% PI: -0.52 to 1.85)
-Using CINeMA, this comparisons was rated as some concerns for heterogeneity. </t>
-  </si>
-  <si>
     <t>Low risk: using CINeMA, this comparison was rated as no concerns for indirectness</t>
   </si>
   <si>
@@ -152,6 +132,26 @@
   </si>
   <si>
     <t>Bias due to study limitations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N=4, n=272;  SMD= -0.01  (95% CI: -0.47 to 0.45, 95% PI: -1.04 to 1.02)
+Using CINeMA, this comparisons was rated as no concerns for heterogeneity. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">N=1, n=42;  SMD= -0.71  (95% CI: -1.79 to 0.37, 95% PI: -2.15 to 0.73)
+Using CINeMA, this comparisons was rated as no concerns for heterogeneity. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">N=7, n=534;  SMD= -0.47  (95% CI: -0.84 to 0.09, 95% PI: -1.46 to 0.53)
+Using CINeMA, this comparisons was rated as major concerns for heterogeneity. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">N=19, n=1092;  SMD= -0.18  (95% CI: -0.41 to -0.05, 95% PI: -1.12 to 0.76)
+Using CINeMA, this comparisons was rated as some concerns for heterogeneity. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">N=1, n=41;  SMD= -0.66  (95% CI: -1.29 to 0.07, 95% PI: -1.85 to 0.52)
+Using CINeMA, this comparisons was rated as some concerns for heterogeneity. </t>
   </si>
 </sst>
 </file>
@@ -545,16 +545,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>0</v>
@@ -571,7 +571,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>9</v>
@@ -580,7 +580,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>10</v>
@@ -594,7 +594,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>9</v>
@@ -603,7 +603,7 @@
         <v>15</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>11</v>
@@ -617,7 +617,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>9</v>
@@ -626,7 +626,7 @@
         <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>12</v>
@@ -640,7 +640,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>9</v>
@@ -649,7 +649,7 @@
         <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>13</v>
@@ -663,7 +663,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>9</v>
@@ -672,7 +672,7 @@
         <v>16</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>14</v>
